--- a/Gastos/Desglose 2027 Presupuestos V5.xlsx
+++ b/Gastos/Desglose 2027 Presupuestos V5.xlsx
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X206"/>
+  <dimension ref="B1:X206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="8" customWidth="1" style="36" min="2" max="2"/>
@@ -2636,40 +2636,40 @@
         </is>
       </c>
       <c r="K24" s="7" t="n">
-        <v>-247571.61</v>
+        <v>-235193.03</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>-480047.38</v>
+        <v>-456045.01</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>-505499.75</v>
+        <v>-480224.76</v>
       </c>
       <c r="N24" s="7" t="n">
-        <v>-391336.67</v>
+        <v>-371769.84</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>-639721.61</v>
+        <v>-607735.53</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>-660412.55</v>
+        <v>-627391.92</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>-425647.17</v>
+        <v>-404364.81</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>-255306.21</v>
+        <v>-242540.9</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>-154533.56</v>
+        <v>-146806.88</v>
       </c>
       <c r="T24" s="7" t="n">
-        <v>-257348.52</v>
+        <v>-244481.09</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>-410647.96</v>
+        <v>-390115.56</v>
       </c>
       <c r="V24" s="7" t="n">
-        <v>-422003.72</v>
+        <v>-400903.53</v>
       </c>
       <c r="W24" s="8">
         <f>SUM(K24:V24)</f>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="X24" s="9" t="inlineStr">
         <is>
-          <t>Presupuesto de Compras 2027: Materias primas según necesidades netas de formulación industrial (-4.850.076,71 € base; 4.995.578,01 € con reserva MOQ 3%).</t>
+          <t>Presupuesto de Compras 2027: Materias primas proyectadas exclusivamente con la subida del +4,5% por inflación prevista (-4.607.572,86 € base con reserva MOQ 3%).</t>
         </is>
       </c>
     </row>
@@ -2726,40 +2726,40 @@
         </is>
       </c>
       <c r="K25" s="7" t="n">
-        <v>-51110.53</v>
+        <v>-48555</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>-99104.56</v>
+        <v>-94149.33</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>-104359.14</v>
+        <v>-99141.17999999999</v>
       </c>
       <c r="N25" s="7" t="n">
-        <v>-80790.46000000001</v>
+        <v>-76750.94</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>-132068.9</v>
+        <v>-125465.45</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>-136340.49</v>
+        <v>-129523.47</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>-87873.77</v>
+        <v>-83480.08</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>-52707.32</v>
+        <v>-50071.95</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>-31903.06</v>
+        <v>-30307.91</v>
       </c>
       <c r="T25" s="7" t="n">
-        <v>-53128.95</v>
+        <v>-50472.5</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>-84777.23</v>
+        <v>-80538.37</v>
       </c>
       <c r="V25" s="7" t="n">
-        <v>-87121.59</v>
+        <v>-82765.50999999999</v>
       </c>
       <c r="W25" s="8">
         <f>SUM(K25:V25)</f>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="X25" s="9" t="inlineStr">
         <is>
-          <t>Presupuesto de Compras 2027: Envases y bidones de envasado (-1.001.286,00 €; 1.031.324,58 € con MOQ 3%).</t>
+          <t>Presupuesto de Compras 2027: Envases y bidones proyectados exclusivamente con +4,5% de inflación (-951.221,69 € con reserva MOQ 3%).</t>
         </is>
       </c>
     </row>
@@ -2906,40 +2906,40 @@
         </is>
       </c>
       <c r="K27" s="7" t="n">
-        <v>-7981.03</v>
+        <v>-7581.98</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>-15475.42</v>
+        <v>-14701.65</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>-16295.93</v>
+        <v>-15481.13</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>-12615.62</v>
+        <v>-11984.84</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>-20622.88</v>
+        <v>-19591.74</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>-21289.9</v>
+        <v>-20225.4</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>-13721.7</v>
+        <v>-13035.61</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>-8230.370000000001</v>
+        <v>-7818.85</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>-4981.74</v>
+        <v>-4732.65</v>
       </c>
       <c r="T27" s="7" t="n">
-        <v>-8296.209999999999</v>
+        <v>-7881.4</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>-13238.17</v>
+        <v>-12576.26</v>
       </c>
       <c r="V27" s="7" t="n">
-        <v>-13604.25</v>
+        <v>-12924.04</v>
       </c>
       <c r="W27" s="8">
         <f>SUM(K27:V27)</f>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="X27" s="9" t="inlineStr">
         <is>
-          <t>Presupuesto de Compras 2027: Etiquetas bobina y adhesivas (-156.353,22 €; 161.043,82 € con MOQ 3%).</t>
+          <t>Presupuesto de Compras 2027: Etiquetas bobina y adhesivas proyectadas con +4,5% de inflación (-148.535,55 € con reserva MOQ 3%).</t>
         </is>
       </c>
     </row>
@@ -2996,40 +2996,40 @@
         </is>
       </c>
       <c r="K28" s="7" t="n">
-        <v>-8300.27</v>
+        <v>-7885.26</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>-16094.43</v>
+        <v>-15289.71</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>-16947.77</v>
+        <v>-16100.38</v>
       </c>
       <c r="N28" s="7" t="n">
-        <v>-13120.25</v>
+        <v>-12464.24</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>-21447.79</v>
+        <v>-20375.4</v>
       </c>
       <c r="P28" s="7" t="n">
-        <v>-22141.49</v>
+        <v>-21034.42</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>-14270.57</v>
+        <v>-13557.04</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>-8559.59</v>
+        <v>-8131.61</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>-5181.01</v>
+        <v>-4921.96</v>
       </c>
       <c r="T28" s="7" t="n">
-        <v>-8628.059999999999</v>
+        <v>-8196.66</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>-13767.69</v>
+        <v>-13079.31</v>
       </c>
       <c r="V28" s="7" t="n">
-        <v>-14148.42</v>
+        <v>-13441</v>
       </c>
       <c r="W28" s="8">
         <f>SUM(K28:V28)</f>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="X28" s="9" t="inlineStr">
         <is>
-          <t>Presupuesto de Compras 2027: Palets homologados nacional y exportación (-162.607,34 €; 167.485,56 € con MOQ 3%).</t>
+          <t>Presupuesto de Compras 2027: Palets homologados proyectados con +4,5% de inflación (-154.476,99 € con reserva MOQ 3%).</t>
         </is>
       </c>
     </row>
@@ -3266,40 +3266,40 @@
         </is>
       </c>
       <c r="K31" s="7" t="n">
-        <v>-4277.83</v>
+        <v>-4063.94</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>-8294.82</v>
+        <v>-7880.08</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>-8734.620000000001</v>
+        <v>-8297.889999999999</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>-6761.97</v>
+        <v>-6423.87</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>-11053.86</v>
+        <v>-10501.17</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>-11411.38</v>
+        <v>-10840.81</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>-7354.83</v>
+        <v>-6987.09</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>-4411.48</v>
+        <v>-4190.91</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>-2670.21</v>
+        <v>-2536.7</v>
       </c>
       <c r="T31" s="7" t="n">
-        <v>-4446.77</v>
+        <v>-4224.43</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>-7095.66</v>
+        <v>-6740.88</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>-7291.88</v>
+        <v>-6927.29</v>
       </c>
       <c r="W31" s="8">
         <f>SUM(K31:V31)</f>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="X31" s="9" t="inlineStr">
         <is>
-          <t>Presupuesto de Compras 2027: Tapones dosificadores y de seguridad (-83.805,31 €; 86.319,47 € con MOQ 3%).</t>
+          <t>Presupuesto de Compras 2027: Tapones dosificadores proyectados con +4,5% de inflación (-79.615,06 € con reserva MOQ 3%).</t>
         </is>
       </c>
     </row>
@@ -19068,7 +19068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="46" customWidth="1" style="36" min="2" max="2"/>
@@ -19092,6 +19092,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="36">
       <c r="B4" s="10" t="inlineStr">
         <is>
@@ -19460,6 +19461,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -19571,6 +19574,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="B27" s="37" t="inlineStr">
         <is>
@@ -19596,6 +19600,7 @@
       <c r="F29" s="43" t="n"/>
       <c r="G29" s="44" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
